--- a/Examples/Example_5_validation_data/data_exa5.xlsx
+++ b/Examples/Example_5_validation_data/data_exa5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artur\PycharmProjects\MT_PEU\Examples\Example_5_validation_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ufbabr-my.sharepoint.com/personal/daniel_diniz_ufba_br/Documents/Projetos/MT-PEU/Examples/Example_5_validation_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110F2CB2-B8E8-44FB-8465-EB743F57268D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{110F2CB2-B8E8-44FB-8465-EB743F57268D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24B315F6-14B9-4095-9994-57864D1E04F8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="independent variable" sheetId="2" r:id="rId1"/>
@@ -23,24 +23,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="58">
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>uY</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>UxTime</t>
-  </si>
-  <si>
-    <t>Temperature</t>
-  </si>
-  <si>
-    <t>Uxtemperature</t>
-  </si>
-  <si>
     <t>120.0</t>
   </si>
   <si>
@@ -195,6 +177,24 @@
   </si>
   <si>
     <t>1.</t>
+  </si>
+  <si>
+    <t>frac</t>
+  </si>
+  <si>
+    <t>ufrac</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>utime</t>
+  </si>
+  <si>
+    <t>temperature</t>
+  </si>
+  <si>
+    <t>utemperature</t>
   </si>
 </sst>
 </file>
@@ -268,15 +268,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,52 +493,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D78D95B7-B7C2-4B1D-A0AA-907023D16FAD}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="5" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:11" ht="13.5">
+    <row r="3" spans="1:11" ht="13.8">
       <c r="A3" s="5" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F3" s="4"/>
       <c r="H3" s="5"/>
@@ -546,406 +546,406 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="5" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="5" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="5" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="5" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="5" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="5" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="5" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="5" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="D27" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H30" s="5"/>
     </row>
@@ -968,276 +968,276 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H42"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="12.75">
+    <row r="1" spans="1:8" ht="13.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="13.5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="13.8">
       <c r="A2" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:8" ht="12.75">
+    <row r="3" spans="1:8" ht="13.2">
       <c r="A3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" ht="13.2">
+      <c r="A4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" ht="13.2">
+      <c r="A5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" ht="13.2">
+      <c r="A6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" ht="13.2">
+      <c r="A7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" ht="13.2">
+      <c r="A8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" ht="13.2">
+      <c r="A9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:8" ht="12.75">
-      <c r="A4" s="5" t="s">
+      <c r="B9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" ht="13.2">
+      <c r="A10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:8" ht="12.75">
-      <c r="A5" s="5" t="s">
+      <c r="B10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" ht="13.2">
+      <c r="A11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" ht="12.75">
-      <c r="A6" s="5" t="s">
+      <c r="B11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" ht="13.2">
+      <c r="A12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" ht="12.75">
-      <c r="A7" s="5" t="s">
+      <c r="B12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" ht="13.2">
+      <c r="A13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" ht="12.75">
-      <c r="A8" s="5" t="s">
+      <c r="B13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" ht="13.2">
+      <c r="A14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" ht="12.75">
-      <c r="A9" s="5" t="s">
+      <c r="B14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" ht="13.2">
+      <c r="A15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" ht="12.75">
-      <c r="A10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" ht="12.75">
-      <c r="A11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" ht="12.75">
-      <c r="A12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" ht="12.75">
-      <c r="A13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" ht="12.75">
-      <c r="A14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" ht="12.75">
-      <c r="A15" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="B15" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D16" s="5"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D17" s="5"/>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D18" s="5"/>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D19" s="5"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D22" s="5"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D23" s="5"/>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D24" s="5"/>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D27" s="5"/>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D28" s="5"/>
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D29" s="5"/>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1">
       <c r="A30" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D30" s="5"/>
     </row>
